--- a/results/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/543-2/5_quantification/543-2_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.5833</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7455</v>
+        <v>3.1042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>306.5833</v>
+        <v>246.0833</v>
       </c>
       <c r="D13" t="n">
-        <v>309.5</v>
+        <v>241</v>
       </c>
       <c r="E13" t="n">
-        <v>89.1673</v>
+        <v>110.0186</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>966.4167</v>
+        <v>792.5</v>
       </c>
       <c r="D14" t="n">
-        <v>929.5</v>
+        <v>779.5</v>
       </c>
       <c r="E14" t="n">
-        <v>189.5389</v>
+        <v>251.8681</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1687.3328</v>
+        <v>2528.4018</v>
       </c>
       <c r="D15" t="n">
-        <v>1266.4158</v>
+        <v>2419.8576</v>
       </c>
       <c r="E15" t="n">
-        <v>1263.5954</v>
+        <v>1628.6442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>62.3333</v>
+        <v>109.25</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>105.5</v>
       </c>
       <c r="E16" t="n">
-        <v>44.9188</v>
+        <v>67.9761</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.4088</v>
+        <v>24.1146</v>
       </c>
       <c r="D17" t="n">
-        <v>28.085</v>
+        <v>23.1195</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2017</v>
+        <v>4.6014</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03474981</v>
+        <v>0.02777727</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03567626</v>
+        <v>0.02861283</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00762422</v>
+        <v>0.01068652</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04342795</v>
+        <v>0.03565817</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04468068</v>
+        <v>0.03431687</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00529377</v>
+        <v>0.009437030000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.3871</v>
+        <v>2.6944</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5267</v>
+        <v>2.8699</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1197</v>
+        <v>1.3388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>232.5</v>
+        <v>193.6667</v>
       </c>
       <c r="D26" t="n">
-        <v>249</v>
+        <v>198.5</v>
       </c>
       <c r="E26" t="n">
-        <v>89.7689</v>
+        <v>115.79</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>572.8333</v>
+        <v>582.6667</v>
       </c>
       <c r="D27" t="n">
-        <v>516</v>
+        <v>607</v>
       </c>
       <c r="E27" t="n">
-        <v>228.2984</v>
+        <v>335.94</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>342.9959</v>
+        <v>275.1036</v>
       </c>
       <c r="D28" t="n">
-        <v>344.528</v>
+        <v>269.4153</v>
       </c>
       <c r="E28" t="n">
-        <v>104.4534</v>
+        <v>124.5421</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1096.3385</v>
+        <v>904.0088</v>
       </c>
       <c r="D29" t="n">
-        <v>1050.655</v>
+        <v>889.4235</v>
       </c>
       <c r="E29" t="n">
-        <v>217.8291</v>
+        <v>284.9078</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.583299999999999</v>
+        <v>6.4167</v>
       </c>
       <c r="D30" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3.4234</v>
+        <v>3.8248</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="D31" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>3.3845</v>
+        <v>4.338</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.5833</v>
+        <v>11.4167</v>
       </c>
       <c r="D32" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>4.5619</v>
+        <v>3.8248</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.9642</v>
+        <v>6.2875</v>
       </c>
       <c r="D33" t="n">
-        <v>4.9169</v>
+        <v>6.2181</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3688</v>
+        <v>0.4432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45785</v>
+        <v>35034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04470139</v>
+        <v>0.03420484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>681</v>
+        <v>776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00066488</v>
+        <v>0.00075763</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>673</v>
+        <v>196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.0312</v>
+        <v>178.7449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.05068186</v>
+        <v>0.03894283</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04470139</v>
+        <v>0.03420484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.818</v>
+        <v>7.0396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1713,7 +1706,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45758</v>
+        <v>35034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1386 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>28.602</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.7369</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>49.088</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>2494</v>
-      </c>
-      <c r="C2" t="n">
-        <v>90.6112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>36.7713</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.4642</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9096</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.4535</v>
-      </c>
-      <c r="I2" t="n">
-        <v>88.1403</v>
-      </c>
-      <c r="J2" t="n">
-        <v>271.1808</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M2" t="n">
-        <v>366</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1178</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1615.5454</v>
-      </c>
-      <c r="P2" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22.1308</v>
-      </c>
-      <c r="R2" t="n">
-        <v>244.4924</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9510</v>
-      </c>
-      <c r="T2" t="n">
-        <v>23791</v>
-      </c>
-      <c r="U2" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.9843</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.0384858</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.04951452</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3.6811</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>319</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>821</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>424.3036</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1357.7098</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5.7452</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3004</v>
-      </c>
-      <c r="C3" t="n">
-        <v>86.0791</v>
-      </c>
-      <c r="D3" t="n">
-        <v>52.8366</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.6292</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.7895</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3181</v>
-      </c>
-      <c r="I3" t="n">
-        <v>207.7913</v>
-      </c>
-      <c r="J3" t="n">
-        <v>919.0333000000001</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M3" t="n">
-        <v>510</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1353</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3672.5811</v>
-      </c>
-      <c r="P3" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25.1547</v>
-      </c>
-      <c r="R3" t="n">
-        <v>295.1198</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10519</v>
-      </c>
-      <c r="T3" t="n">
-        <v>26271</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.0484837</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.05150166</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.0661</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>373</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>954</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>578.8721</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1536.7809</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.916</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1698</v>
-      </c>
-      <c r="C4" t="n">
-        <v>63.4601</v>
-      </c>
-      <c r="D4" t="n">
-        <v>34.3535</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.8473</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8408</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5365</v>
-      </c>
-      <c r="I4" t="n">
-        <v>257.4252</v>
-      </c>
-      <c r="J4" t="n">
-        <v>340.8051</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="n">
-        <v>316</v>
-      </c>
-      <c r="N4" t="n">
-        <v>919</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1009.4478</v>
-      </c>
-      <c r="P4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>28.8414</v>
-      </c>
-      <c r="R4" t="n">
-        <v>172.8944</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7548</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18977</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.04186539</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.04842704</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5.7839</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>246</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>472</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>346.9066</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1040.7199</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.683</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1631</v>
-      </c>
-      <c r="C5" t="n">
-        <v>87.5017</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30.956</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.8266</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9353</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="I5" t="n">
-        <v>297.0319</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38.7695</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>305</v>
-      </c>
-      <c r="N5" t="n">
-        <v>695</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1016.0925</v>
-      </c>
-      <c r="P5" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19.5402</v>
-      </c>
-      <c r="R5" t="n">
-        <v>232.5513</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8756</v>
-      </c>
-      <c r="T5" t="n">
-        <v>18925</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.9575</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.7927999999999999</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.03483326</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.03672391</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.4401</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>266</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>560</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>342.1493</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>776.3402</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.5694</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1204</v>
-      </c>
-      <c r="C6" t="n">
-        <v>55.3793</v>
-      </c>
-      <c r="D6" t="n">
-        <v>28.6478</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.9331</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8558</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9177</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1008</v>
-      </c>
-      <c r="I6" t="n">
-        <v>394.2633</v>
-      </c>
-      <c r="J6" t="n">
-        <v>364.613</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>256</v>
-      </c>
-      <c r="N6" t="n">
-        <v>826</v>
-      </c>
-      <c r="O6" t="n">
-        <v>509.0021</v>
-      </c>
-      <c r="P6" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>28.2779</v>
-      </c>
-      <c r="R6" t="n">
-        <v>154.267</v>
-      </c>
-      <c r="S6" t="n">
-        <v>7010</v>
-      </c>
-      <c r="T6" t="n">
-        <v>17818</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.03651926</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.04635762</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.5929</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>158</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>403</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>283.6934</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>949.3768</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.5138</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2066</v>
-      </c>
-      <c r="C7" t="n">
-        <v>81.29900000000001</v>
-      </c>
-      <c r="D7" t="n">
-        <v>34.8468</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9035</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8619</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1545</v>
-      </c>
-      <c r="I7" t="n">
-        <v>472.2469</v>
-      </c>
-      <c r="J7" t="n">
-        <v>745.5315000000001</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>314</v>
-      </c>
-      <c r="N7" t="n">
-        <v>898</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1516.7392</v>
-      </c>
-      <c r="P7" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>30.3348</v>
-      </c>
-      <c r="R7" t="n">
-        <v>231.7645</v>
-      </c>
-      <c r="S7" t="n">
-        <v>9080</v>
-      </c>
-      <c r="T7" t="n">
-        <v>22988</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.0345815</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.03906386</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.0203</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>298</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>636</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>356.3919</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1018.0631</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.0764</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1233</v>
-      </c>
-      <c r="C8" t="n">
-        <v>57.0332</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27.8479</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.048</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8727</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9278</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="I8" t="n">
-        <v>459.3869</v>
-      </c>
-      <c r="J8" t="n">
-        <v>484.8297</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>136</v>
-      </c>
-      <c r="N8" t="n">
-        <v>718</v>
-      </c>
-      <c r="O8" t="n">
-        <v>352.664</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>35.2664</v>
-      </c>
-      <c r="R8" t="n">
-        <v>155.9239</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7017</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19168</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.0193815</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.03745826</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2827</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>217</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>147.397</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>816.8964999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.9559</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2066</v>
-      </c>
-      <c r="C9" t="n">
-        <v>100.4483</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26.9826</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.7227</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9631999999999999</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.9018</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="I9" t="n">
-        <v>550.2623</v>
-      </c>
-      <c r="J9" t="n">
-        <v>877.6099</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>357</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1078</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3205.0836</v>
-      </c>
-      <c r="P9" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>31.1173</v>
-      </c>
-      <c r="R9" t="n">
-        <v>254.2498</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9429</v>
-      </c>
-      <c r="T9" t="n">
-        <v>23720</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03786192</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.04544688</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.9331</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>308</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>871</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>407.333</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1232.1585</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.3945</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2656</v>
-      </c>
-      <c r="C10" t="n">
-        <v>108.8378</v>
-      </c>
-      <c r="D10" t="n">
-        <v>32.5449</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.3442</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9542</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8877</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.0333</v>
-      </c>
-      <c r="I10" t="n">
-        <v>642.811</v>
-      </c>
-      <c r="J10" t="n">
-        <v>193.3272</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>250</v>
-      </c>
-      <c r="N10" t="n">
-        <v>940</v>
-      </c>
-      <c r="O10" t="n">
-        <v>568.7595</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>25.8527</v>
-      </c>
-      <c r="R10" t="n">
-        <v>277.0782</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10094</v>
-      </c>
-      <c r="T10" t="n">
-        <v>25807</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.02476719</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.03642423</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.1655</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>159</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>360</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>267.9239</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1060.59</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.3122</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2113</v>
-      </c>
-      <c r="C11" t="n">
-        <v>91.9731</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30.2288</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.0426</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9444</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9135</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0369</v>
-      </c>
-      <c r="I11" t="n">
-        <v>728.2953</v>
-      </c>
-      <c r="J11" t="n">
-        <v>633.991</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>288</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1033</v>
-      </c>
-      <c r="O11" t="n">
-        <v>826.2397</v>
-      </c>
-      <c r="P11" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>25.0376</v>
-      </c>
-      <c r="R11" t="n">
-        <v>227.6224</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8939</v>
-      </c>
-      <c r="T11" t="n">
-        <v>23523</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.03221837</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.04391447</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3.0753</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>193</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>429</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>317.1076</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1157.1047</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.8602</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2173</v>
-      </c>
-      <c r="C12" t="n">
-        <v>86.8531</v>
-      </c>
-      <c r="D12" t="n">
-        <v>32.2149</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.6961</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9287</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.9358</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>787.1661</v>
-      </c>
-      <c r="J12" t="n">
-        <v>480.0667</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>336</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1082</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3947.6004</v>
-      </c>
-      <c r="P12" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>29.4597</v>
-      </c>
-      <c r="R12" t="n">
-        <v>225.5219</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8872</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23390</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.03787196</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.04625909</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.9907</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>252</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>720</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>369.1787</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1216.4306</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>4.9177</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C13" t="n">
-        <v>68.5432</v>
-      </c>
-      <c r="D13" t="n">
-        <v>38.3841</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.7857</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8285</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.9402</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.1037</v>
-      </c>
-      <c r="I13" t="n">
-        <v>859.4817</v>
-      </c>
-      <c r="J13" t="n">
-        <v>288.0416</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>245</v>
-      </c>
-      <c r="N13" t="n">
-        <v>877</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2008.2388</v>
-      </c>
-      <c r="P13" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>27.8922</v>
-      </c>
-      <c r="R13" t="n">
-        <v>193.7229</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8132</v>
-      </c>
-      <c r="T13" t="n">
-        <v>21901</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.03012789</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.04004383</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3.6134</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>167</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>431</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>274.6934</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>993.8915</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.6258</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -3165,6 +2179,1399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C2" t="n">
+        <v>90.6112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.7713</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.4642</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9096</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="I2" t="n">
+        <v>88.1403</v>
+      </c>
+      <c r="J2" t="n">
+        <v>271.1808</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>367</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3847.8725</v>
+      </c>
+      <c r="P2" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23.4626</v>
+      </c>
+      <c r="R2" t="n">
+        <v>244.4924</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9510</v>
+      </c>
+      <c r="T2" t="n">
+        <v>23791</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.03859096</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.04947249</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.2721</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>321</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>981</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>419.0904</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1354.2834</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.9587</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3004</v>
+      </c>
+      <c r="C3" t="n">
+        <v>86.0791</v>
+      </c>
+      <c r="D3" t="n">
+        <v>52.8366</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.6292</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7895</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="I3" t="n">
+        <v>207.7913</v>
+      </c>
+      <c r="J3" t="n">
+        <v>919.0333000000001</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>457</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1251</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2524.4693</v>
+      </c>
+      <c r="P3" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.5767</v>
+      </c>
+      <c r="R3" t="n">
+        <v>295.1198</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10519</v>
+      </c>
+      <c r="T3" t="n">
+        <v>26271</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.04344519</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.04761905</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.7273</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>390</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1139</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>509.2325</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1408.1291</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.985</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1698</v>
+      </c>
+      <c r="C4" t="n">
+        <v>63.4601</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.3535</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.8473</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8408</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5365</v>
+      </c>
+      <c r="I4" t="n">
+        <v>257.4252</v>
+      </c>
+      <c r="J4" t="n">
+        <v>340.8051</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>268</v>
+      </c>
+      <c r="N4" t="n">
+        <v>843</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2315.246</v>
+      </c>
+      <c r="P4" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24.6303</v>
+      </c>
+      <c r="R4" t="n">
+        <v>172.8944</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7548</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18977</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03550609</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.0444222</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.2055</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>207</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>667</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>299.2498</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>975.7910000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6.2014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C5" t="n">
+        <v>87.5017</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30.956</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.8266</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9353</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="I5" t="n">
+        <v>297.0319</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.7695</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>316</v>
+      </c>
+      <c r="N5" t="n">
+        <v>643</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1132.4478</v>
+      </c>
+      <c r="P5" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16.4123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>232.5513</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8756</v>
+      </c>
+      <c r="T5" t="n">
+        <v>18925</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.03608954</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03397622</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.4401</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>289</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>547</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>352.4214</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>716.6711</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.4451</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="C6" t="n">
+        <v>55.3793</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.6478</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.9331</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9177</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="I6" t="n">
+        <v>394.2633</v>
+      </c>
+      <c r="J6" t="n">
+        <v>364.613</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>168</v>
+      </c>
+      <c r="N6" t="n">
+        <v>539</v>
+      </c>
+      <c r="O6" t="n">
+        <v>955.6072</v>
+      </c>
+      <c r="P6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>21.2357</v>
+      </c>
+      <c r="R6" t="n">
+        <v>154.267</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7010</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17818</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.02396576</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.03025031</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.5929</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>101</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>337</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>182.1249</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>626.4701</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.1518</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2066</v>
+      </c>
+      <c r="C7" t="n">
+        <v>81.29900000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>34.8468</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9035</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="I7" t="n">
+        <v>472.2469</v>
+      </c>
+      <c r="J7" t="n">
+        <v>745.5315000000001</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>302</v>
+      </c>
+      <c r="N7" t="n">
+        <v>926</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4481.1589</v>
+      </c>
+      <c r="P7" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24.7578</v>
+      </c>
+      <c r="R7" t="n">
+        <v>231.7645</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9080</v>
+      </c>
+      <c r="T7" t="n">
+        <v>22988</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.03325991</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04028189</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.4518</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>288</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>831</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>344.1493</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1058.8204</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.5064</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C8" t="n">
+        <v>57.0332</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27.8479</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I8" t="n">
+        <v>459.3869</v>
+      </c>
+      <c r="J8" t="n">
+        <v>484.8297</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>87</v>
+      </c>
+      <c r="N8" t="n">
+        <v>597</v>
+      </c>
+      <c r="O8" t="n">
+        <v>684.4996</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>31.1136</v>
+      </c>
+      <c r="R8" t="n">
+        <v>155.9239</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7017</v>
+      </c>
+      <c r="T8" t="n">
+        <v>19168</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01239846</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.03114566</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>95.598</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>677.4285</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.5916</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2066</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100.4483</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.9826</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.7227</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9018</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="I9" t="n">
+        <v>550.2623</v>
+      </c>
+      <c r="J9" t="n">
+        <v>877.6099</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>115</v>
+      </c>
+      <c r="N9" t="n">
+        <v>503</v>
+      </c>
+      <c r="O9" t="n">
+        <v>170.2965</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>34.0593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>254.2498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9429</v>
+      </c>
+      <c r="T9" t="n">
+        <v>23720</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01219642</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.02120573</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>132.2965</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>584.529</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.1981</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2656</v>
+      </c>
+      <c r="C10" t="n">
+        <v>108.8378</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32.5449</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.3442</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8877</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>642.811</v>
+      </c>
+      <c r="J10" t="n">
+        <v>193.3272</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>162</v>
+      </c>
+      <c r="N10" t="n">
+        <v>510</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2778.7089</v>
+      </c>
+      <c r="P10" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.7763</v>
+      </c>
+      <c r="R10" t="n">
+        <v>277.0782</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10094</v>
+      </c>
+      <c r="T10" t="n">
+        <v>25807</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01604914</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01976208</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.8045</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>146</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>385</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>178.5391</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>579.2447</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.4019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2113</v>
+      </c>
+      <c r="C11" t="n">
+        <v>91.9731</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30.2288</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.0426</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9444</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="I11" t="n">
+        <v>728.2953</v>
+      </c>
+      <c r="J11" t="n">
+        <v>633.991</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>214</v>
+      </c>
+      <c r="N11" t="n">
+        <v>810</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4436.6908</v>
+      </c>
+      <c r="P11" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24.9252</v>
+      </c>
+      <c r="R11" t="n">
+        <v>227.6224</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8939</v>
+      </c>
+      <c r="T11" t="n">
+        <v>23523</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02394004</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03443438</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.6359</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>683</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>239.5807</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>918.1808</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>6.9788</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C12" t="n">
+        <v>86.8531</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32.2149</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.6961</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>787.1661</v>
+      </c>
+      <c r="J12" t="n">
+        <v>480.0667</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>315</v>
+      </c>
+      <c r="N12" t="n">
+        <v>962</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5019.4259</v>
+      </c>
+      <c r="P12" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.5086</v>
+      </c>
+      <c r="R12" t="n">
+        <v>225.5219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8872</v>
+      </c>
+      <c r="T12" t="n">
+        <v>23390</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.03550496</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.04112869</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.1039</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>227</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>851</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>351.5929</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1087.8915</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6.2349</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>68.5432</v>
+      </c>
+      <c r="D13" t="n">
+        <v>38.3841</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.7857</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9402</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="I13" t="n">
+        <v>859.4817</v>
+      </c>
+      <c r="J13" t="n">
+        <v>288.0416</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>182</v>
+      </c>
+      <c r="N13" t="n">
+        <v>749</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1994.3982</v>
+      </c>
+      <c r="P13" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>21.9165</v>
+      </c>
+      <c r="R13" t="n">
+        <v>193.7229</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8132</v>
+      </c>
+      <c r="T13" t="n">
+        <v>21901</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.02238072</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.03419935</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.0648</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>112</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>390</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>197.3675</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>860.6661</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.7961</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3185,7 +3592,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/543-2/5_quantification/543-2_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>3.5833</v>
       </c>
       <c r="D12" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1042</v>
+        <v>3.6045</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>246.0833</v>
+        <v>272.1667</v>
       </c>
       <c r="D13" t="n">
-        <v>241</v>
+        <v>256.5</v>
       </c>
       <c r="E13" t="n">
-        <v>110.0186</v>
+        <v>103.0153</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>792.5</v>
+        <v>859.1667</v>
       </c>
       <c r="D14" t="n">
-        <v>779.5</v>
+        <v>823</v>
       </c>
       <c r="E14" t="n">
-        <v>251.8681</v>
+        <v>218.9815</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2528.4018</v>
+        <v>2731.1689</v>
       </c>
       <c r="D15" t="n">
-        <v>2419.8576</v>
+        <v>3304.1613</v>
       </c>
       <c r="E15" t="n">
-        <v>1628.6442</v>
+        <v>1933.1012</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>109.25</v>
+        <v>127</v>
       </c>
       <c r="D16" t="n">
-        <v>105.5</v>
+        <v>164.5</v>
       </c>
       <c r="E16" t="n">
-        <v>67.9761</v>
+        <v>85.1181</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.1146</v>
+        <v>17.4441</v>
       </c>
       <c r="D17" t="n">
-        <v>23.1195</v>
+        <v>20.2255</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6014</v>
+        <v>8.3163</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02777727</v>
+        <v>0.0309508</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02861283</v>
+        <v>0.03282185</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01068652</v>
+        <v>0.01025355</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03565817</v>
+        <v>0.03889819</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03431687</v>
+        <v>0.03848694</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009437030000000001</v>
+        <v>0.008797559999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6944</v>
+        <v>1.5461</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8699</v>
+        <v>0.9871</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3388</v>
+        <v>1.4925</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>193.6667</v>
+        <v>220</v>
       </c>
       <c r="D26" t="n">
-        <v>198.5</v>
+        <v>195.5</v>
       </c>
       <c r="E26" t="n">
-        <v>115.79</v>
+        <v>114.3464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>582.6667</v>
+        <v>642.75</v>
       </c>
       <c r="D27" t="n">
-        <v>607</v>
+        <v>643.5</v>
       </c>
       <c r="E27" t="n">
-        <v>335.94</v>
+        <v>313.6695</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>275.1036</v>
+        <v>306.1293</v>
       </c>
       <c r="D28" t="n">
-        <v>269.4153</v>
+        <v>282.8945</v>
       </c>
       <c r="E28" t="n">
-        <v>124.5421</v>
+        <v>117.4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>904.0088</v>
+        <v>981.0484</v>
       </c>
       <c r="D29" t="n">
-        <v>889.4235</v>
+        <v>946.9357</v>
       </c>
       <c r="E29" t="n">
-        <v>284.9078</v>
+        <v>253.3438</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.4167</v>
+        <v>7.1667</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3.8248</v>
+        <v>3.639</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>9.916700000000001</v>
+      </c>
+      <c r="D31" t="n">
         <v>9.5</v>
       </c>
-      <c r="D31" t="n">
-        <v>9</v>
-      </c>
       <c r="E31" t="n">
-        <v>4.338</v>
+        <v>3.5537</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.4167</v>
+        <v>12.3333</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3.8248</v>
+        <v>2.7414</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.2875</v>
+        <v>7.346</v>
       </c>
       <c r="D33" t="n">
-        <v>6.2181</v>
+        <v>7.335</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4432</v>
+        <v>0.4175</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35034</v>
+        <v>37787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03420484</v>
+        <v>0.03689268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>776</v>
+        <v>923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00075763</v>
+        <v>0.00090116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>178.7449</v>
+        <v>220.9766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03894283</v>
+        <v>0.04200993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03420484</v>
+        <v>0.03689268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>465</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03689268</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03734668</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.0396</v>
+        <v>7.8995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1726,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35034</v>
+        <v>37787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.602</v>
+        <v>26.1351</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.7369</v>
+        <v>4.3547</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.088</v>
+        <v>49.2081</v>
       </c>
     </row>
     <row r="12">
@@ -1949,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0487</v>
+        <v>50.0471</v>
       </c>
     </row>
     <row r="13">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5744</v>
+        <v>0.5177</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4256</v>
+        <v>0.4823</v>
       </c>
     </row>
     <row r="15">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2150,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2165,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.3257</v>
       </c>
     </row>
   </sheetData>
@@ -2384,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="N2" t="n">
-        <v>1177</v>
+        <v>1290</v>
       </c>
       <c r="O2" t="n">
-        <v>3847.8725</v>
+        <v>4721.1416</v>
       </c>
       <c r="P2" t="n">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.4626</v>
+        <v>22.6978</v>
       </c>
       <c r="R2" t="n">
         <v>244.4924</v>
@@ -2417,28 +2497,28 @@
         <v>0.9843</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03859096</v>
+        <v>0.04300736</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04947249</v>
+        <v>0.05422218</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.2721</v>
+        <v>4.4991</v>
       </c>
       <c r="Z2" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="AA2" t="n">
-        <v>981</v>
+        <v>1129</v>
       </c>
       <c r="AB2" t="n">
-        <v>419.0904</v>
+        <v>473.4752</v>
       </c>
       <c r="AC2" t="n">
-        <v>1354.2834</v>
+        <v>1493.9819</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>16</v>
@@ -2447,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.9587</v>
+        <v>7.7397</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>457</v>
       </c>
       <c r="N3" t="n">
-        <v>1251</v>
+        <v>1211</v>
       </c>
       <c r="O3" t="n">
-        <v>2524.4693</v>
+        <v>3119.447</v>
       </c>
       <c r="P3" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.5767</v>
+        <v>19.3754</v>
       </c>
       <c r="R3" t="n">
         <v>295.1198</v>
@@ -2521,34 +2601,34 @@
         <v>0.04344519</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04761905</v>
+        <v>0.04609646</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.7273</v>
+        <v>0.6777</v>
       </c>
       <c r="Z3" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AA3" t="n">
-        <v>1139</v>
+        <v>1106</v>
       </c>
       <c r="AB3" t="n">
-        <v>509.2325</v>
+        <v>507.8478</v>
       </c>
       <c r="AC3" t="n">
-        <v>1408.1291</v>
+        <v>1366.46</v>
       </c>
       <c r="AD3" t="n">
         <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.985</v>
+        <v>7.0795</v>
       </c>
     </row>
     <row r="4">
@@ -2586,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="N4" t="n">
-        <v>843</v>
+        <v>861</v>
       </c>
       <c r="O4" t="n">
-        <v>2315.246</v>
+        <v>433.0488</v>
       </c>
       <c r="P4" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.6303</v>
+        <v>19.684</v>
       </c>
       <c r="R4" t="n">
         <v>172.8944</v>
@@ -2619,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03550609</v>
+        <v>0.03842077</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0444222</v>
+        <v>0.04537071</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.2055</v>
+        <v>0.5784</v>
       </c>
       <c r="Z4" t="n">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="AA4" t="n">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="AB4" t="n">
-        <v>299.2498</v>
+        <v>326.4924</v>
       </c>
       <c r="AC4" t="n">
-        <v>975.7910000000001</v>
+        <v>989.9209</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.2014</v>
+        <v>7.2793</v>
       </c>
     </row>
     <row r="5">
@@ -2687,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="N5" t="n">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="O5" t="n">
-        <v>1132.4478</v>
+        <v>1327.9575</v>
       </c>
       <c r="P5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.4123</v>
+        <v>18.9708</v>
       </c>
       <c r="R5" t="n">
         <v>232.5513</v>
@@ -2720,37 +2800,37 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03608954</v>
+        <v>0.03962997</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03397622</v>
+        <v>0.03556143</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.4401</v>
+        <v>3.0101</v>
       </c>
       <c r="Z5" t="n">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="AA5" t="n">
-        <v>547</v>
+        <v>618</v>
       </c>
       <c r="AB5" t="n">
-        <v>352.4214</v>
+        <v>394.8061</v>
       </c>
       <c r="AC5" t="n">
-        <v>716.6711</v>
+        <v>756.8133</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>11</v>
       </c>
       <c r="AF5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.4451</v>
+        <v>6.8501</v>
       </c>
     </row>
     <row r="6">
@@ -2788,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="N6" t="n">
-        <v>539</v>
+        <v>827</v>
       </c>
       <c r="O6" t="n">
-        <v>955.6072</v>
+        <v>4633.9457</v>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.2357</v>
+        <v>21.7556</v>
       </c>
       <c r="R6" t="n">
         <v>154.267</v>
@@ -2821,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02396576</v>
+        <v>0.0363766</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03025031</v>
+        <v>0.04641374</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5929</v>
+        <v>1.2965</v>
       </c>
       <c r="Z6" t="n">
-        <v>101</v>
+        <v>188</v>
       </c>
       <c r="AA6" t="n">
-        <v>337</v>
+        <v>574</v>
       </c>
       <c r="AB6" t="n">
-        <v>182.1249</v>
+        <v>279.8234</v>
       </c>
       <c r="AC6" t="n">
-        <v>626.4701</v>
+        <v>956.6783</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.1518</v>
+        <v>7.0853</v>
       </c>
     </row>
     <row r="7">
@@ -2892,19 +2972,19 @@
         <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="N7" t="n">
-        <v>926</v>
+        <v>1001</v>
       </c>
       <c r="O7" t="n">
-        <v>4481.1589</v>
+        <v>5050.6635</v>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.7578</v>
+        <v>22.9576</v>
       </c>
       <c r="R7" t="n">
         <v>231.7645</v>
@@ -2922,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03325991</v>
+        <v>0.03656388</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04028189</v>
+        <v>0.04354446</v>
       </c>
       <c r="Y7" t="n">
         <v>3.4518</v>
       </c>
       <c r="Z7" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="AA7" t="n">
-        <v>831</v>
+        <v>979</v>
       </c>
       <c r="AB7" t="n">
-        <v>344.1493</v>
+        <v>379.8772</v>
       </c>
       <c r="AC7" t="n">
-        <v>1058.8204</v>
+        <v>1148.9331</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.5064</v>
+        <v>7.6495</v>
       </c>
     </row>
     <row r="8">
@@ -2990,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="N8" t="n">
-        <v>597</v>
+        <v>707</v>
       </c>
       <c r="O8" t="n">
-        <v>684.4996</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.1136</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>155.9239</v>
@@ -3023,13 +3103,13 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01239846</v>
+        <v>0.01524868</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03114566</v>
+        <v>0.03688439</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6413</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>24</v>
@@ -3038,22 +3118,22 @@
         <v>98</v>
       </c>
       <c r="AB8" t="n">
-        <v>95.598</v>
+        <v>119.3259</v>
       </c>
       <c r="AC8" t="n">
-        <v>677.4285</v>
+        <v>803.926</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.5916</v>
+        <v>7.3907</v>
       </c>
     </row>
     <row r="9">
@@ -3091,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N9" t="n">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="O9" t="n">
-        <v>170.2965</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.0593</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>254.2498</v>
@@ -3124,28 +3204,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01219642</v>
+        <v>0.01389331</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02120573</v>
+        <v>0.02179595</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3933</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="AA9" t="n">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="AB9" t="n">
-        <v>132.2965</v>
+        <v>151.7817</v>
       </c>
       <c r="AC9" t="n">
-        <v>584.529</v>
+        <v>596.2864</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -3154,7 +3234,7 @@
         <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.1981</v>
+        <v>7.4614</v>
       </c>
     </row>
     <row r="10">
@@ -3192,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="N10" t="n">
-        <v>510</v>
+        <v>819</v>
       </c>
       <c r="O10" t="n">
-        <v>2778.7089</v>
+        <v>4442.9507</v>
       </c>
       <c r="P10" t="n">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.7763</v>
+        <v>22.6681</v>
       </c>
       <c r="R10" t="n">
         <v>277.0782</v>
@@ -3225,37 +3305,37 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01604914</v>
+        <v>0.02298395</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01976208</v>
+        <v>0.03173558</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8045</v>
+        <v>1.4436</v>
       </c>
       <c r="Z10" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="AA10" t="n">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="AB10" t="n">
-        <v>178.5391</v>
+        <v>253.9239</v>
       </c>
       <c r="AC10" t="n">
-        <v>579.2447</v>
+        <v>937.193</v>
       </c>
       <c r="AD10" t="n">
         <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.4019</v>
+        <v>7.4338</v>
       </c>
     </row>
     <row r="11">
@@ -3296,19 +3376,19 @@
         <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N11" t="n">
-        <v>810</v>
+        <v>735</v>
       </c>
       <c r="O11" t="n">
-        <v>4436.6908</v>
+        <v>3854.2623</v>
       </c>
       <c r="P11" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.9252</v>
+        <v>22.5395</v>
       </c>
       <c r="R11" t="n">
         <v>227.6224</v>
@@ -3326,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02394004</v>
+        <v>0.02349256</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03443438</v>
+        <v>0.03124601</v>
       </c>
       <c r="Y11" t="n">
         <v>2.6359</v>
       </c>
       <c r="Z11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AA11" t="n">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="AB11" t="n">
-        <v>239.5807</v>
+        <v>234.5097</v>
       </c>
       <c r="AC11" t="n">
-        <v>918.1808</v>
+        <v>828.0559</v>
       </c>
       <c r="AD11" t="n">
         <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.9788</v>
+        <v>8.2616</v>
       </c>
     </row>
     <row r="12">
@@ -3394,22 +3474,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>315</v>
+        <v>258</v>
       </c>
       <c r="N12" t="n">
-        <v>962</v>
+        <v>791</v>
       </c>
       <c r="O12" t="n">
-        <v>5019.4259</v>
+        <v>3488.8755</v>
       </c>
       <c r="P12" t="n">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.5086</v>
+        <v>20.7671</v>
       </c>
       <c r="R12" t="n">
         <v>225.5219</v>
@@ -3427,37 +3507,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03550496</v>
+        <v>0.02908025</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04112869</v>
+        <v>0.03381787</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.1039</v>
+        <v>0.4434</v>
       </c>
       <c r="Z12" t="n">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="AA12" t="n">
-        <v>851</v>
+        <v>688</v>
       </c>
       <c r="AB12" t="n">
-        <v>351.5929</v>
+        <v>285.9655</v>
       </c>
       <c r="AC12" t="n">
-        <v>1087.8915</v>
+        <v>883.1686</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.2349</v>
+        <v>7.2076</v>
       </c>
     </row>
     <row r="13">
@@ -3495,22 +3575,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="N13" t="n">
-        <v>749</v>
+        <v>878</v>
       </c>
       <c r="O13" t="n">
-        <v>1994.3982</v>
+        <v>1701.7342</v>
       </c>
       <c r="P13" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.9165</v>
+        <v>17.913</v>
       </c>
       <c r="R13" t="n">
         <v>193.7229</v>
@@ -3528,37 +3608,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02238072</v>
+        <v>0.02926709</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03419935</v>
+        <v>0.04008949</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.0648</v>
+        <v>0.5162</v>
       </c>
       <c r="Z13" t="n">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="n">
-        <v>390</v>
+        <v>464</v>
       </c>
       <c r="AB13" t="n">
-        <v>197.3675</v>
+        <v>265.7229</v>
       </c>
       <c r="AC13" t="n">
-        <v>860.6661</v>
+        <v>1011.1636</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.7961</v>
+        <v>6.7133</v>
       </c>
     </row>
   </sheetData>

--- a/results/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/543-2/5_quantification/543-2_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.5833</v>
+        <v>5.9167</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6045</v>
+        <v>3.7285</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>272.1667</v>
+        <v>271.5833</v>
       </c>
       <c r="D13" t="n">
         <v>256.5</v>
       </c>
       <c r="E13" t="n">
-        <v>103.0153</v>
+        <v>101.7791</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>859.1667</v>
+        <v>855.0833</v>
       </c>
       <c r="D14" t="n">
         <v>823</v>
       </c>
       <c r="E14" t="n">
-        <v>218.9815</v>
+        <v>211.8333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2731.1689</v>
+        <v>2755.2291</v>
       </c>
       <c r="D15" t="n">
-        <v>3304.1613</v>
+        <v>2967.4308</v>
       </c>
       <c r="E15" t="n">
-        <v>1933.1012</v>
+        <v>1834.2435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>127</v>
+        <v>128.4167</v>
       </c>
       <c r="D16" t="n">
-        <v>164.5</v>
+        <v>136</v>
       </c>
       <c r="E16" t="n">
-        <v>85.1181</v>
+        <v>82.4659</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.4441</v>
+        <v>19.5274</v>
       </c>
       <c r="D17" t="n">
-        <v>20.2255</v>
+        <v>21.8175</v>
       </c>
       <c r="E17" t="n">
-        <v>8.3163</v>
+        <v>6.3195</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0309508</v>
+        <v>0.0308937</v>
       </c>
       <c r="D23" t="n">
         <v>0.03282185</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01025355</v>
+        <v>0.01016454</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03889819</v>
+        <v>0.03874315</v>
       </c>
       <c r="D24" t="n">
         <v>0.03848694</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008797559999999999</v>
+        <v>0.00865819</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.5461</v>
+        <v>2.63</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9871</v>
+        <v>2.5869</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4925</v>
+        <v>1.5678</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>220</v>
+        <v>220.3333</v>
       </c>
       <c r="D26" t="n">
-        <v>195.5</v>
+        <v>196</v>
       </c>
       <c r="E26" t="n">
-        <v>114.3464</v>
+        <v>114.9342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>642.75</v>
+        <v>638.6667</v>
       </c>
       <c r="D27" t="n">
-        <v>643.5</v>
+        <v>645</v>
       </c>
       <c r="E27" t="n">
-        <v>313.6695</v>
+        <v>307.1912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>306.1293</v>
+        <v>305.5257</v>
       </c>
       <c r="D28" t="n">
         <v>282.8945</v>
       </c>
       <c r="E28" t="n">
-        <v>117.4412</v>
+        <v>116.1175</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>981.0484</v>
+        <v>976.5997</v>
       </c>
       <c r="D29" t="n">
         <v>946.9357</v>
       </c>
       <c r="E29" t="n">
-        <v>253.3438</v>
+        <v>245.8595</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.1667</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3.639</v>
+        <v>3.3303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.3333</v>
+        <v>12.25</v>
       </c>
       <c r="D32" t="n">
         <v>11.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2.7414</v>
+        <v>2.6328</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.346</v>
+        <v>7.3971</v>
       </c>
       <c r="D33" t="n">
-        <v>7.335</v>
+        <v>7.4123</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4175</v>
+        <v>0.428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37787</v>
+        <v>37700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03689268</v>
+        <v>0.03680774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>220.9766</v>
+        <v>221.7647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04200993</v>
+        <v>0.04191481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03689268</v>
+        <v>0.03680774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03689268</v>
+        <v>0.03680774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03734668</v>
+        <v>0.03726174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.8995</v>
+        <v>7.9055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37787</v>
+        <v>37700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.1351</v>
+        <v>26.3801</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.3547</v>
+        <v>5.1772</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.2081</v>
+        <v>49.3094</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5177</v>
+        <v>0.5218</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4823</v>
+        <v>0.4782</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>409</v>
@@ -2473,13 +2473,13 @@
         <v>1290</v>
       </c>
       <c r="O2" t="n">
-        <v>4721.1416</v>
+        <v>4651.4431</v>
       </c>
       <c r="P2" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.6978</v>
+        <v>22.4707</v>
       </c>
       <c r="R2" t="n">
         <v>244.4924</v>
@@ -2503,7 +2503,7 @@
         <v>0.05422218</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4991</v>
+        <v>4.9081</v>
       </c>
       <c r="Z2" t="n">
         <v>346</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="N3" t="n">
-        <v>1211</v>
+        <v>1161</v>
       </c>
       <c r="O3" t="n">
         <v>3119.447</v>
@@ -2598,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04344519</v>
+        <v>0.04268467</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04609646</v>
+        <v>0.04419322</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6777</v>
+        <v>1.6942</v>
       </c>
       <c r="Z3" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AA3" t="n">
-        <v>1106</v>
+        <v>1056</v>
       </c>
       <c r="AB3" t="n">
-        <v>507.8478</v>
+        <v>499.1909</v>
       </c>
       <c r="AC3" t="n">
-        <v>1366.46</v>
+        <v>1311.2468</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.0795</v>
+        <v>7.2445</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N4" t="n">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O4" t="n">
-        <v>433.0488</v>
+        <v>905.9382000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.684</v>
+        <v>22.0961</v>
       </c>
       <c r="R4" t="n">
         <v>172.8944</v>
@@ -2699,25 +2699,25 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03842077</v>
+        <v>0.0381558</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04537071</v>
+        <v>0.04526532</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5784</v>
+        <v>2.8919</v>
       </c>
       <c r="Z4" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AA4" t="n">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="AB4" t="n">
-        <v>326.4924</v>
+        <v>324.9066</v>
       </c>
       <c r="AC4" t="n">
-        <v>989.9209</v>
+        <v>988.3351</v>
       </c>
       <c r="AD4" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.2793</v>
+        <v>7.4857</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N5" t="n">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O5" t="n">
-        <v>1327.9575</v>
+        <v>1174.5189</v>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.9708</v>
+        <v>18.0695</v>
       </c>
       <c r="R5" t="n">
         <v>232.5513</v>
@@ -2800,25 +2800,25 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03962997</v>
+        <v>0.03985838</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03556143</v>
+        <v>0.03566711</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.0101</v>
+        <v>4.7301</v>
       </c>
       <c r="Z5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA5" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AB5" t="n">
-        <v>394.8061</v>
+        <v>396.3919</v>
       </c>
       <c r="AC5" t="n">
-        <v>756.8133</v>
+        <v>758.8133</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
@@ -2830,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.8501</v>
+        <v>6.9562</v>
       </c>
     </row>
     <row r="6">
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
         <v>255</v>
@@ -2877,13 +2877,13 @@
         <v>827</v>
       </c>
       <c r="O6" t="n">
-        <v>4633.9457</v>
+        <v>4342.0929</v>
       </c>
       <c r="P6" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.7556</v>
+        <v>22.1535</v>
       </c>
       <c r="R6" t="n">
         <v>154.267</v>
@@ -2907,7 +2907,7 @@
         <v>0.04641374</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2965</v>
+        <v>2.5929</v>
       </c>
       <c r="Z6" t="n">
         <v>188</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
         <v>332</v>
@@ -2978,13 +2978,13 @@
         <v>1001</v>
       </c>
       <c r="O7" t="n">
-        <v>5050.6635</v>
+        <v>5093.8056</v>
       </c>
       <c r="P7" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.9576</v>
+        <v>22.6391</v>
       </c>
       <c r="R7" t="n">
         <v>231.7645</v>
@@ -3008,7 +3008,7 @@
         <v>0.04354446</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.4518</v>
+        <v>4.3147</v>
       </c>
       <c r="Z7" t="n">
         <v>315</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>131</v>
@@ -3180,13 +3180,13 @@
         <v>517</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>339.5929</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>22.6395</v>
       </c>
       <c r="R9" t="n">
         <v>254.2498</v>
@@ -3210,7 +3210,7 @@
         <v>0.02179595</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.3933</v>
       </c>
       <c r="Z9" t="n">
         <v>69</v>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>232</v>
@@ -3281,13 +3281,13 @@
         <v>819</v>
       </c>
       <c r="O10" t="n">
-        <v>4442.9507</v>
+        <v>2911.7384</v>
       </c>
       <c r="P10" t="n">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.6681</v>
+        <v>21.5684</v>
       </c>
       <c r="R10" t="n">
         <v>277.0782</v>
@@ -3311,7 +3311,7 @@
         <v>0.03173558</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4436</v>
+        <v>2.1655</v>
       </c>
       <c r="Z10" t="n">
         <v>163</v>
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N11" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O11" t="n">
-        <v>3854.2623</v>
+        <v>3023.1232</v>
       </c>
       <c r="P11" t="n">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.5395</v>
+        <v>22.0666</v>
       </c>
       <c r="R11" t="n">
         <v>227.6224</v>
@@ -3406,25 +3406,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02349256</v>
+        <v>0.02360443</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03124601</v>
+        <v>0.03128853</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.6359</v>
+        <v>3.5146</v>
       </c>
       <c r="Z11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA11" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AB11" t="n">
-        <v>234.5097</v>
+        <v>235.9239</v>
       </c>
       <c r="AC11" t="n">
-        <v>828.0559</v>
+        <v>829.4701</v>
       </c>
       <c r="AD11" t="n">
         <v>5</v>
@@ -3436,7 +3436,7 @@
         <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.2616</v>
+        <v>8.398</v>
       </c>
     </row>
     <row r="12">
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>258</v>
@@ -3483,13 +3483,13 @@
         <v>791</v>
       </c>
       <c r="O12" t="n">
-        <v>3488.8755</v>
+        <v>5141.7447</v>
       </c>
       <c r="P12" t="n">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="Q12" t="n">
-        <v>20.7671</v>
+        <v>21.4239</v>
       </c>
       <c r="R12" t="n">
         <v>225.5219</v>
@@ -3513,7 +3513,7 @@
         <v>0.03381787</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4434</v>
+        <v>1.7737</v>
       </c>
       <c r="Z12" t="n">
         <v>202</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>238</v>
@@ -3584,13 +3584,13 @@
         <v>878</v>
       </c>
       <c r="O13" t="n">
-        <v>1701.7342</v>
+        <v>2359.3048</v>
       </c>
       <c r="P13" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="Q13" t="n">
-        <v>17.913</v>
+        <v>19.8261</v>
       </c>
       <c r="R13" t="n">
         <v>193.7229</v>
@@ -3614,7 +3614,7 @@
         <v>0.04008949</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5162</v>
+        <v>2.581</v>
       </c>
       <c r="Z13" t="n">
         <v>165</v>

--- a/results/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/543-2/5_quantification/543-2_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.9167</v>
+        <v>7.6667</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7285</v>
+        <v>3.1718</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>271.5833</v>
+        <v>340.4167</v>
       </c>
       <c r="D13" t="n">
-        <v>256.5</v>
+        <v>359.5</v>
       </c>
       <c r="E13" t="n">
-        <v>101.7791</v>
+        <v>123.6604</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>855.0833</v>
+        <v>984.4167</v>
       </c>
       <c r="D14" t="n">
-        <v>823</v>
+        <v>931</v>
       </c>
       <c r="E14" t="n">
-        <v>211.8333</v>
+        <v>246.9455</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2755.2291</v>
+        <v>3155.5841</v>
       </c>
       <c r="D15" t="n">
-        <v>2967.4308</v>
+        <v>2646.9713</v>
       </c>
       <c r="E15" t="n">
-        <v>1834.2435</v>
+        <v>1753.2852</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>128.4167</v>
+        <v>146.4167</v>
       </c>
       <c r="D16" t="n">
-        <v>136</v>
+        <v>128.5</v>
       </c>
       <c r="E16" t="n">
-        <v>82.4659</v>
+        <v>81.8518</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.5274</v>
+        <v>21.9862</v>
       </c>
       <c r="D17" t="n">
-        <v>21.8175</v>
+        <v>21.5468</v>
       </c>
       <c r="E17" t="n">
-        <v>6.3195</v>
+        <v>3.0031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0308937</v>
+        <v>0.0386731</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03282185</v>
+        <v>0.04027366</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01016454</v>
+        <v>0.01198052</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03874315</v>
+        <v>0.04434147</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03848694</v>
+        <v>0.04618375</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00865819</v>
+        <v>0.008761929999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.63</v>
+        <v>3.3796</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5869</v>
+        <v>3.7115</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5678</v>
+        <v>1.1821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>220.3333</v>
+        <v>287.5833</v>
       </c>
       <c r="D26" t="n">
-        <v>196</v>
+        <v>300.5</v>
       </c>
       <c r="E26" t="n">
-        <v>114.9342</v>
+        <v>140.6527</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>638.6667</v>
+        <v>794.5</v>
       </c>
       <c r="D27" t="n">
-        <v>645</v>
+        <v>712</v>
       </c>
       <c r="E27" t="n">
-        <v>307.1912</v>
+        <v>325.9293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>305.5257</v>
+        <v>384.5349</v>
       </c>
       <c r="D28" t="n">
-        <v>282.8945</v>
+        <v>401.1995</v>
       </c>
       <c r="E28" t="n">
-        <v>116.1175</v>
+        <v>143.337</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>976.5997</v>
+        <v>1125.117</v>
       </c>
       <c r="D29" t="n">
-        <v>946.9357</v>
+        <v>1075.155</v>
       </c>
       <c r="E29" t="n">
-        <v>245.8595</v>
+        <v>287.2318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>3.3303</v>
+        <v>3.6139</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.916700000000001</v>
+        <v>11.8333</v>
       </c>
       <c r="D31" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>3.5537</v>
+        <v>3.4333</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.25</v>
+        <v>13.9167</v>
       </c>
       <c r="D32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>2.6328</v>
+        <v>4.1878</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.3971</v>
+        <v>7.5002</v>
       </c>
       <c r="D33" t="n">
-        <v>7.4123</v>
+        <v>7.53</v>
       </c>
       <c r="E33" t="n">
-        <v>0.428</v>
+        <v>0.4024</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37700</v>
+        <v>40374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03680774</v>
+        <v>0.03941846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>923</v>
+        <v>1018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00090116</v>
+        <v>0.00099391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>221.7647</v>
+        <v>260.4774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04191481</v>
+        <v>0.04490581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03680774</v>
+        <v>0.03941846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03680774</v>
+        <v>0.03941846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03726174</v>
+        <v>0.03987245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.9055</v>
+        <v>8.0052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.4721</v>
+        <v>5.6569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37700</v>
+        <v>40374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>619</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.3801</v>
+        <v>21.9008</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.1772</v>
+        <v>3.6496</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.3094</v>
+        <v>46.0542</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0471</v>
+        <v>50.0487</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5218</v>
+        <v>0.4298</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4782</v>
+        <v>0.5702</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.5814</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2464,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="N2" t="n">
-        <v>1290</v>
+        <v>1316</v>
       </c>
       <c r="O2" t="n">
-        <v>4651.4431</v>
+        <v>4215.5832</v>
       </c>
       <c r="P2" t="n">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.4707</v>
+        <v>21.8424</v>
       </c>
       <c r="R2" t="n">
         <v>244.4924</v>
@@ -2497,25 +2497,25 @@
         <v>0.9843</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04300736</v>
+        <v>0.04574132</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05422218</v>
+        <v>0.05531504</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.9081</v>
+        <v>4.4991</v>
       </c>
       <c r="Z2" t="n">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="AA2" t="n">
-        <v>1129</v>
+        <v>1151</v>
       </c>
       <c r="AB2" t="n">
-        <v>473.4752</v>
+        <v>501.9605</v>
       </c>
       <c r="AC2" t="n">
-        <v>1493.9819</v>
+        <v>1522.4672</v>
       </c>
       <c r="AD2" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.7397</v>
+        <v>7.6346</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>449</v>
+        <v>627</v>
       </c>
       <c r="N3" t="n">
-        <v>1161</v>
+        <v>1506</v>
       </c>
       <c r="O3" t="n">
-        <v>3119.447</v>
+        <v>6168.7539</v>
       </c>
       <c r="P3" t="n">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.3754</v>
+        <v>20.911</v>
       </c>
       <c r="R3" t="n">
         <v>295.1198</v>
@@ -2598,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04268467</v>
+        <v>0.05960643</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04419322</v>
+        <v>0.05732557</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.6942</v>
+        <v>4.405</v>
       </c>
       <c r="Z3" t="n">
-        <v>413</v>
+        <v>620</v>
       </c>
       <c r="AA3" t="n">
-        <v>1056</v>
+        <v>1467</v>
       </c>
       <c r="AB3" t="n">
-        <v>499.1909</v>
+        <v>714.4996</v>
       </c>
       <c r="AC3" t="n">
-        <v>1311.2468</v>
+        <v>1720.1657</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.2445</v>
+        <v>7.2576</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="N4" t="n">
-        <v>859</v>
+        <v>930</v>
       </c>
       <c r="O4" t="n">
-        <v>905.9382000000001</v>
+        <v>2010.7413</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.0961</v>
+        <v>22.3416</v>
       </c>
       <c r="R4" t="n">
         <v>172.8944</v>
@@ -2699,28 +2699,28 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0381558</v>
+        <v>0.0463699</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04526532</v>
+        <v>0.04900669</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.8919</v>
+        <v>4.6271</v>
       </c>
       <c r="Z4" t="n">
-        <v>234</v>
+        <v>314</v>
       </c>
       <c r="AA4" t="n">
-        <v>686</v>
+        <v>757</v>
       </c>
       <c r="AB4" t="n">
-        <v>324.9066</v>
+        <v>394.2914</v>
       </c>
       <c r="AC4" t="n">
-        <v>988.3351</v>
+        <v>1069.1341</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>12</v>
@@ -2729,7 +2729,7 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.4857</v>
+        <v>7.6209</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="N5" t="n">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="O5" t="n">
-        <v>1174.5189</v>
+        <v>1195.8326</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.0695</v>
+        <v>17.8482</v>
       </c>
       <c r="R5" t="n">
         <v>232.5513</v>
@@ -2800,37 +2800,37 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03985838</v>
+        <v>0.0416857</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03566711</v>
+        <v>0.03651255</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.7301</v>
+        <v>4.3001</v>
       </c>
       <c r="Z5" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AA5" t="n">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AB5" t="n">
-        <v>396.3919</v>
+        <v>410.0488</v>
       </c>
       <c r="AC5" t="n">
-        <v>758.8133</v>
+        <v>772.4701</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.9562</v>
+        <v>6.9142</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>255</v>
+        <v>362</v>
       </c>
       <c r="N6" t="n">
-        <v>827</v>
+        <v>932</v>
       </c>
       <c r="O6" t="n">
-        <v>4342.0929</v>
+        <v>4654.0289</v>
       </c>
       <c r="P6" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.1535</v>
+        <v>21.2513</v>
       </c>
       <c r="R6" t="n">
         <v>154.267</v>
@@ -2901,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0363766</v>
+        <v>0.05164051</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04641374</v>
+        <v>0.05230666</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5929</v>
+        <v>3.8894</v>
       </c>
       <c r="Z6" t="n">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AA6" t="n">
-        <v>574</v>
+        <v>634</v>
       </c>
       <c r="AB6" t="n">
-        <v>279.8234</v>
+        <v>405.9066</v>
       </c>
       <c r="AC6" t="n">
-        <v>956.6783</v>
+        <v>1081.1758</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.0853</v>
+        <v>7.3821</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="N7" t="n">
-        <v>1001</v>
+        <v>1035</v>
       </c>
       <c r="O7" t="n">
-        <v>5093.8056</v>
+        <v>3670.0247</v>
       </c>
       <c r="P7" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.6391</v>
+        <v>24.1449</v>
       </c>
       <c r="R7" t="n">
         <v>231.7645</v>
@@ -3002,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03656388</v>
+        <v>0.04030837</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04354446</v>
+        <v>0.04502349</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3147</v>
+        <v>3.8833</v>
       </c>
       <c r="Z7" t="n">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="AA7" t="n">
-        <v>979</v>
+        <v>1013</v>
       </c>
       <c r="AB7" t="n">
-        <v>379.8772</v>
+        <v>418.6051</v>
       </c>
       <c r="AC7" t="n">
-        <v>1148.9331</v>
+        <v>1187.661</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -3032,7 +3032,7 @@
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.6495</v>
+        <v>7.4392</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="N8" t="n">
-        <v>707</v>
+        <v>746</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>719.0854</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>29.9619</v>
       </c>
       <c r="R8" t="n">
         <v>155.9239</v>
@@ -3103,28 +3103,28 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01524868</v>
+        <v>0.01895397</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03688439</v>
+        <v>0.03891903</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.6413</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="AA8" t="n">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="AB8" t="n">
-        <v>119.3259</v>
+        <v>150.7107</v>
       </c>
       <c r="AC8" t="n">
-        <v>803.926</v>
+        <v>851.725</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -3133,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.3907</v>
+        <v>7.3183</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>131</v>
+        <v>373</v>
       </c>
       <c r="N9" t="n">
-        <v>517</v>
+        <v>1123</v>
       </c>
       <c r="O9" t="n">
-        <v>339.5929</v>
+        <v>1938.3738</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.6395</v>
+        <v>19.5795</v>
       </c>
       <c r="R9" t="n">
         <v>254.2498</v>
@@ -3204,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01389331</v>
+        <v>0.03955881</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02179595</v>
+        <v>0.04734401</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3933</v>
+        <v>3.5398</v>
       </c>
       <c r="Z9" t="n">
-        <v>69</v>
+        <v>345</v>
       </c>
       <c r="AA9" t="n">
-        <v>287</v>
+        <v>937</v>
       </c>
       <c r="AB9" t="n">
-        <v>151.7817</v>
+        <v>430.9188</v>
       </c>
       <c r="AC9" t="n">
-        <v>596.2864</v>
+        <v>1287.188</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4614</v>
+        <v>7.8895</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N10" t="n">
-        <v>819</v>
+        <v>783</v>
       </c>
       <c r="O10" t="n">
-        <v>2911.7384</v>
+        <v>2932.3952</v>
       </c>
       <c r="P10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5684</v>
+        <v>21.2492</v>
       </c>
       <c r="R10" t="n">
         <v>277.0782</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02298395</v>
+        <v>0.02288488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03173558</v>
+        <v>0.03034061</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1655</v>
+        <v>2.5264</v>
       </c>
       <c r="Z10" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AA10" t="n">
-        <v>413</v>
+        <v>367</v>
       </c>
       <c r="AB10" t="n">
-        <v>253.9239</v>
+        <v>255.9949</v>
       </c>
       <c r="AC10" t="n">
-        <v>937.193</v>
+        <v>900.1219</v>
       </c>
       <c r="AD10" t="n">
         <v>5</v>
@@ -3335,7 +3335,7 @@
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.4338</v>
+        <v>7.8752</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="N11" t="n">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="O11" t="n">
-        <v>3023.1232</v>
+        <v>2208.055</v>
       </c>
       <c r="P11" t="n">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.0666</v>
+        <v>23.0006</v>
       </c>
       <c r="R11" t="n">
         <v>227.6224</v>
@@ -3406,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02360443</v>
+        <v>0.02696051</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03128853</v>
+        <v>0.03213876</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5146</v>
+        <v>3.0753</v>
       </c>
       <c r="Z11" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="AA11" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="AB11" t="n">
-        <v>235.9239</v>
+        <v>261.0244</v>
       </c>
       <c r="AC11" t="n">
-        <v>829.4701</v>
+        <v>836.9138</v>
       </c>
       <c r="AD11" t="n">
         <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.398</v>
+        <v>8.1534</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3474,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>258</v>
+        <v>357</v>
       </c>
       <c r="N12" t="n">
-        <v>791</v>
+        <v>1110</v>
       </c>
       <c r="O12" t="n">
-        <v>5141.7447</v>
+        <v>5792.5874</v>
       </c>
       <c r="P12" t="n">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.4239</v>
+        <v>21.8588</v>
       </c>
       <c r="R12" t="n">
         <v>225.5219</v>
@@ -3507,37 +3507,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02908025</v>
+        <v>0.04023895</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03381787</v>
+        <v>0.04745618</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7737</v>
+        <v>3.1039</v>
       </c>
       <c r="Z12" t="n">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="AA12" t="n">
-        <v>688</v>
+        <v>938</v>
       </c>
       <c r="AB12" t="n">
-        <v>285.9655</v>
+        <v>396.4924</v>
       </c>
       <c r="AC12" t="n">
-        <v>883.1686</v>
+        <v>1252.9747</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.2076</v>
+        <v>7.7386</v>
       </c>
     </row>
     <row r="13">
@@ -3575,22 +3575,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N13" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="O13" t="n">
-        <v>2359.3048</v>
+        <v>2361.5475</v>
       </c>
       <c r="P13" t="n">
         <v>119</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.8261</v>
+        <v>19.8449</v>
       </c>
       <c r="R13" t="n">
         <v>193.7229</v>
@@ -3608,28 +3608,28 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02926709</v>
+        <v>0.03012789</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04008949</v>
+        <v>0.04040911</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.581</v>
+        <v>2.0648</v>
       </c>
       <c r="Z13" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="AA13" t="n">
-        <v>464</v>
+        <v>658</v>
       </c>
       <c r="AB13" t="n">
-        <v>265.7229</v>
+        <v>273.9655</v>
       </c>
       <c r="AC13" t="n">
-        <v>1011.1636</v>
+        <v>1019.4062</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
@@ -3638,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.7133</v>
+        <v>6.7793</v>
       </c>
     </row>
   </sheetData>

--- a/results/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/543-2/5_quantification/543-2_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.6667</v>
+        <v>8.5</v>
       </c>
       <c r="D12" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1718</v>
+        <v>2.7798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>340.4167</v>
+        <v>369.5833</v>
       </c>
       <c r="D13" t="n">
-        <v>359.5</v>
+        <v>363.5</v>
       </c>
       <c r="E13" t="n">
-        <v>123.6604</v>
+        <v>87.4252</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>984.4167</v>
+        <v>1061.5833</v>
       </c>
       <c r="D14" t="n">
-        <v>931</v>
+        <v>1079.5</v>
       </c>
       <c r="E14" t="n">
-        <v>246.9455</v>
+        <v>212.4226</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3155.5841</v>
+        <v>3482.7054</v>
       </c>
       <c r="D15" t="n">
-        <v>2646.9713</v>
+        <v>3215.7516</v>
       </c>
       <c r="E15" t="n">
-        <v>1753.2852</v>
+        <v>1346.7996</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>146.4167</v>
+        <v>161</v>
       </c>
       <c r="D16" t="n">
-        <v>128.5</v>
+        <v>150</v>
       </c>
       <c r="E16" t="n">
-        <v>81.8518</v>
+        <v>63.6025</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.9862</v>
+        <v>21.6333</v>
       </c>
       <c r="D17" t="n">
-        <v>21.5468</v>
+        <v>21.4151</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0031</v>
+        <v>2.0651</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0386731</v>
+        <v>0.04190314</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04027366</v>
+        <v>0.04165666</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01198052</v>
+        <v>0.00587647</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04434147</v>
+        <v>0.04754696</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04618375</v>
+        <v>0.04808305</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008761929999999999</v>
+        <v>0.00496234</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.3796</v>
+        <v>3.7455</v>
       </c>
       <c r="D25" t="n">
-        <v>3.7115</v>
+        <v>3.6373</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1821</v>
+        <v>0.6692</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>287.5833</v>
+        <v>326.75</v>
       </c>
       <c r="D26" t="n">
-        <v>300.5</v>
+        <v>323.5</v>
       </c>
       <c r="E26" t="n">
-        <v>140.6527</v>
+        <v>91.0236</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>794.5</v>
+        <v>931.0833</v>
       </c>
       <c r="D27" t="n">
-        <v>712</v>
+        <v>929.5</v>
       </c>
       <c r="E27" t="n">
-        <v>325.9293</v>
+        <v>231.7312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>384.5349</v>
+        <v>417.2165</v>
       </c>
       <c r="D28" t="n">
-        <v>401.1995</v>
+        <v>409.099</v>
       </c>
       <c r="E28" t="n">
-        <v>143.337</v>
+        <v>101.1174</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1125.117</v>
+        <v>1213.0975</v>
       </c>
       <c r="D29" t="n">
-        <v>1075.155</v>
+        <v>1229.2971</v>
       </c>
       <c r="E29" t="n">
-        <v>287.2318</v>
+        <v>244.0405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.833299999999999</v>
+        <v>9.75</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3.6139</v>
+        <v>2.9886</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.8333</v>
+        <v>12.8333</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>3.4333</v>
+        <v>2.7907</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.9167</v>
+        <v>14.3333</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="E32" t="n">
-        <v>4.1878</v>
+        <v>3.7009</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>19.0833</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.662100000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.5002</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.4024</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.701</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.7684</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40374</v>
+        <v>44105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03941846</v>
+        <v>0.04306115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1018</v>
+        <v>1118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00099391</v>
+        <v>0.00109154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>260.4774</v>
+        <v>294.0333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04490581</v>
+        <v>0.04903999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03941846</v>
+        <v>0.04306115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03941846</v>
+        <v>0.04306115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03987245</v>
+        <v>0.04351515</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>275</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2231</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.0052</v>
+        <v>8.023999999999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40374</v>
+        <v>44105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>677</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.9008</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +2117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.6496</v>
+        <v>2.0952</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.0542</v>
+        <v>43.6709</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0487</v>
+        <v>50.0417</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4298</v>
+        <v>0.3456</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5702</v>
+        <v>0.6544</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="N2" t="n">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="O2" t="n">
-        <v>4215.5832</v>
+        <v>4276.3111</v>
       </c>
       <c r="P2" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.8424</v>
+        <v>21.0656</v>
       </c>
       <c r="R2" t="n">
         <v>244.4924</v>
@@ -2497,28 +2625,28 @@
         <v>0.9843</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04574132</v>
+        <v>0.04721346</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05531504</v>
+        <v>0.05586146</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4991</v>
+        <v>4.9081</v>
       </c>
       <c r="Z2" t="n">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="AA2" t="n">
-        <v>1151</v>
+        <v>1261</v>
       </c>
       <c r="AB2" t="n">
-        <v>501.9605</v>
+        <v>511.5462</v>
       </c>
       <c r="AC2" t="n">
-        <v>1522.4672</v>
+        <v>1532.053</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>16</v>
@@ -2527,7 +2655,13 @@
         <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.6346</v>
+        <v>7.9755</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.5567</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2699,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="N3" t="n">
-        <v>1506</v>
+        <v>1428</v>
       </c>
       <c r="O3" t="n">
-        <v>6168.7539</v>
+        <v>5687.4208</v>
       </c>
       <c r="P3" t="n">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.911</v>
+        <v>20.833</v>
       </c>
       <c r="R3" t="n">
         <v>295.1198</v>
@@ -2598,37 +2732,43 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05960643</v>
+        <v>0.05333207</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05732557</v>
+        <v>0.05435651</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.405</v>
+        <v>3.7273</v>
       </c>
       <c r="Z3" t="n">
-        <v>620</v>
+        <v>506</v>
       </c>
       <c r="AA3" t="n">
-        <v>1467</v>
+        <v>1323</v>
       </c>
       <c r="AB3" t="n">
-        <v>714.4996</v>
+        <v>636.8011</v>
       </c>
       <c r="AC3" t="n">
-        <v>1720.1657</v>
+        <v>1628.4672</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.2576</v>
+        <v>7.2256</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4286</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="N4" t="n">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="O4" t="n">
-        <v>2010.7413</v>
+        <v>2053.6825</v>
       </c>
       <c r="P4" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.3416</v>
+        <v>23.0751</v>
       </c>
       <c r="R4" t="n">
         <v>172.8944</v>
@@ -2699,28 +2839,28 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0463699</v>
+        <v>0.04478007</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04900669</v>
+        <v>0.04874322</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6271</v>
+        <v>3.4703</v>
       </c>
       <c r="Z4" t="n">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="AA4" t="n">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="AB4" t="n">
-        <v>394.2914</v>
+        <v>381.463</v>
       </c>
       <c r="AC4" t="n">
-        <v>1069.1341</v>
+        <v>1062.4773</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>12</v>
@@ -2729,7 +2869,13 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.6209</v>
+        <v>7.8081</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3596</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="N5" t="n">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="O5" t="n">
-        <v>1195.8326</v>
+        <v>1205.8326</v>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.8482</v>
+        <v>17.2262</v>
       </c>
       <c r="R5" t="n">
         <v>232.5513</v>
@@ -2800,37 +2946,43 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0416857</v>
+        <v>0.04351302</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03651255</v>
+        <v>0.03746367</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.3001</v>
+        <v>3.8701</v>
       </c>
       <c r="Z5" t="n">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="AA5" t="n">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="AB5" t="n">
-        <v>410.0488</v>
+        <v>428.5341</v>
       </c>
       <c r="AC5" t="n">
-        <v>772.4701</v>
+        <v>792.9554000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.9142</v>
+        <v>7.1387</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.2286</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +3020,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>362</v>
+        <v>279</v>
       </c>
       <c r="N6" t="n">
-        <v>932</v>
+        <v>853</v>
       </c>
       <c r="O6" t="n">
-        <v>4654.0289</v>
+        <v>3453.51</v>
       </c>
       <c r="P6" t="n">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.2513</v>
+        <v>21.4504</v>
       </c>
       <c r="R6" t="n">
         <v>154.267</v>
@@ -2901,37 +3053,43 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05164051</v>
+        <v>0.03980029</v>
       </c>
       <c r="X6" t="n">
-        <v>0.05230666</v>
+        <v>0.04787294</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8894</v>
+        <v>3.2411</v>
       </c>
       <c r="Z6" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="AA6" t="n">
-        <v>634</v>
+        <v>589</v>
       </c>
       <c r="AB6" t="n">
-        <v>405.9066</v>
+        <v>308.4802</v>
       </c>
       <c r="AC6" t="n">
-        <v>1081.1758</v>
+        <v>987.7494</v>
       </c>
       <c r="AD6" t="n">
         <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.3821</v>
+        <v>8.0304</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5652</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +3127,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="N7" t="n">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="O7" t="n">
-        <v>3670.0247</v>
+        <v>2330.3982</v>
       </c>
       <c r="P7" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.1449</v>
+        <v>21.3798</v>
       </c>
       <c r="R7" t="n">
         <v>231.7645</v>
@@ -3002,28 +3160,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04030837</v>
+        <v>0.03898678</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04502349</v>
+        <v>0.04450148</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.8833</v>
+        <v>4.3147</v>
       </c>
       <c r="Z7" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="AA7" t="n">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="AB7" t="n">
-        <v>418.6051</v>
+        <v>403.7056</v>
       </c>
       <c r="AC7" t="n">
-        <v>1187.661</v>
+        <v>1172.7615</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -3032,7 +3190,13 @@
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.4392</v>
+        <v>7.4527</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4404</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3234,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="N8" t="n">
-        <v>746</v>
+        <v>842</v>
       </c>
       <c r="O8" t="n">
-        <v>719.0854</v>
+        <v>2977.9932</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.9619</v>
+        <v>26.3539</v>
       </c>
       <c r="R8" t="n">
         <v>155.9239</v>
@@ -3103,37 +3267,43 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01895397</v>
+        <v>0.03120992</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03891903</v>
+        <v>0.04392738</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6413</v>
+        <v>2.5654</v>
       </c>
       <c r="Z8" t="n">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="AA8" t="n">
-        <v>317</v>
+        <v>749</v>
       </c>
       <c r="AB8" t="n">
-        <v>150.7107</v>
+        <v>245.7523</v>
       </c>
       <c r="AC8" t="n">
-        <v>851.725</v>
+        <v>961.4945</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.3183</v>
+        <v>8.156000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3274</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
-        <v>373</v>
+        <v>425</v>
       </c>
       <c r="N9" t="n">
-        <v>1123</v>
+        <v>1180</v>
       </c>
       <c r="O9" t="n">
-        <v>1938.3738</v>
+        <v>2941.2237</v>
       </c>
       <c r="P9" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.5795</v>
+        <v>21.7868</v>
       </c>
       <c r="R9" t="n">
         <v>254.2498</v>
@@ -3204,28 +3374,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03955881</v>
+        <v>0.04507371</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04734401</v>
+        <v>0.04974705</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.5398</v>
+        <v>4.7198</v>
       </c>
       <c r="Z9" t="n">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="AA9" t="n">
-        <v>937</v>
+        <v>1032</v>
       </c>
       <c r="AB9" t="n">
-        <v>430.9188</v>
+        <v>489.3036</v>
       </c>
       <c r="AC9" t="n">
-        <v>1287.188</v>
+        <v>1348.5017</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -3234,7 +3404,13 @@
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.8895</v>
+        <v>7.8171</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.5037</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
-        <v>231</v>
+        <v>373</v>
       </c>
       <c r="N10" t="n">
-        <v>783</v>
+        <v>1172</v>
       </c>
       <c r="O10" t="n">
-        <v>2932.3952</v>
+        <v>4403.7253</v>
       </c>
       <c r="P10" t="n">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2492</v>
+        <v>21.9091</v>
       </c>
       <c r="R10" t="n">
         <v>277.0782</v>
@@ -3305,37 +3481,43 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02288488</v>
+        <v>0.03695265</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03034061</v>
+        <v>0.04541403</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5264</v>
+        <v>3.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="AA10" t="n">
-        <v>367</v>
+        <v>837</v>
       </c>
       <c r="AB10" t="n">
-        <v>255.9949</v>
+        <v>414.4924</v>
       </c>
       <c r="AC10" t="n">
-        <v>900.1219</v>
+        <v>1345.9991</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.8752</v>
+        <v>7.7288</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.4677</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>241</v>
+        <v>333</v>
       </c>
       <c r="N11" t="n">
-        <v>756</v>
+        <v>1136</v>
       </c>
       <c r="O11" t="n">
-        <v>2208.055</v>
+        <v>5377.3965</v>
       </c>
       <c r="P11" t="n">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.0006</v>
+        <v>21.3389</v>
       </c>
       <c r="R11" t="n">
         <v>227.6224</v>
@@ -3406,37 +3588,43 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02696051</v>
+        <v>0.03725249</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03213876</v>
+        <v>0.04829316</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.0753</v>
+        <v>3.5146</v>
       </c>
       <c r="Z11" t="n">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="AA11" t="n">
-        <v>667</v>
+        <v>1084</v>
       </c>
       <c r="AB11" t="n">
-        <v>261.0244</v>
+        <v>377.7351</v>
       </c>
       <c r="AC11" t="n">
-        <v>836.9138</v>
+        <v>1285.8326</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.1534</v>
+        <v>8.2704</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>35</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.5278</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="N12" t="n">
-        <v>1110</v>
+        <v>1177</v>
       </c>
       <c r="O12" t="n">
-        <v>5792.5874</v>
+        <v>4218.4461</v>
       </c>
       <c r="P12" t="n">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.8588</v>
+        <v>22.5585</v>
       </c>
       <c r="R12" t="n">
         <v>225.5219</v>
@@ -3507,37 +3695,43 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04023895</v>
+        <v>0.04598738</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04745618</v>
+        <v>0.05032065</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.1039</v>
+        <v>3.5473</v>
       </c>
       <c r="Z12" t="n">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="AA12" t="n">
-        <v>938</v>
+        <v>1041</v>
       </c>
       <c r="AB12" t="n">
-        <v>396.4924</v>
+        <v>456.6051</v>
       </c>
       <c r="AC12" t="n">
-        <v>1252.9747</v>
+        <v>1330.259</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.7386</v>
+        <v>7.5027</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.4118</v>
       </c>
     </row>
     <row r="13">
@@ -3575,22 +3769,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="N13" t="n">
-        <v>885</v>
+        <v>965</v>
       </c>
       <c r="O13" t="n">
-        <v>2361.5475</v>
+        <v>2866.5252</v>
       </c>
       <c r="P13" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.8449</v>
+        <v>20.6225</v>
       </c>
       <c r="R13" t="n">
         <v>193.7229</v>
@@ -3608,37 +3802,43 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03012789</v>
+        <v>0.03873586</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04040911</v>
+        <v>0.04406191</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.0648</v>
+        <v>3.0972</v>
       </c>
       <c r="Z13" t="n">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="AA13" t="n">
-        <v>658</v>
+        <v>858</v>
       </c>
       <c r="AB13" t="n">
-        <v>273.9655</v>
+        <v>352.1787</v>
       </c>
       <c r="AC13" t="n">
-        <v>1019.4062</v>
+        <v>1108.6194</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.7793</v>
+        <v>7.3062</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.4388</v>
       </c>
     </row>
   </sheetData>
